--- a/output/pdf_financials_xlsx/NSU.xlsx
+++ b/output/pdf_financials_xlsx/NSU.xlsx
@@ -2518,19 +2518,19 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.064267</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.119866</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.444859</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.439776</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.8166679999999999</v>
       </c>
     </row>
     <row r="93">
@@ -3985,7 +3985,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -4510,7 +4514,11 @@
           <t>Reserves 13</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -4914,7 +4922,11 @@
           <t>Reserve 4</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" s="5" t="n">
         <v>0.064267</v>
       </c>

--- a/output/pdf_financials_xlsx/NSU.xlsx
+++ b/output/pdf_financials_xlsx/NSU.xlsx
@@ -675,7 +675,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000919</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -1025,7 +1025,7 @@
         <v>-0.5577490000000001</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-4.171564</v>
+        <v>-4.172483</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-1.765826</v>
@@ -1069,7 +1069,7 @@
         <v>-0.5577490000000001</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-4.171564</v>
+        <v>-4.172483</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-1.765826</v>
@@ -1178,19 +1178,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.290059</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.16636</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.42595</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.137313</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>2.22374</v>
       </c>
     </row>
     <row r="35">
@@ -1222,19 +1222,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.290059</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.16636</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.42595</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.137313</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>2.22374</v>
       </c>
     </row>
     <row r="37">
@@ -1486,19 +1486,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.290059</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.16636</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.773944</v>
+        <v>0.347994</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.158419</v>
+        <v>0.021106</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2.252856</v>
+        <v>0.029116</v>
       </c>
     </row>
     <row r="49">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">
@@ -9749,7 +9749,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">

--- a/output/pdf_financials_xlsx/NSU.xlsx
+++ b/output/pdf_financials_xlsx/NSU.xlsx
@@ -559,19 +559,19 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.01</v>
+        <v>0.012713</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.088214</v>
+        <v>0.089057</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.215322</v>
+        <v>0.248447</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.454565</v>
+        <v>0.535551</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.499532</v>
+        <v>0.5643629999999999</v>
       </c>
     </row>
     <row r="8">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.01</v>
+        <v>0.012713</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>0.5577490000000001</v>
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.01</v>
+        <v>-0.012713</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>-0.5577490000000001</v>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.003639</v>
       </c>
       <c r="C101" s="3" t="n">
         <v>-0.024212</v>
@@ -2821,7 +2821,7 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.044759</v>
+        <v>0.04112</v>
       </c>
       <c r="C106" s="3" t="n">
         <v>0.105089</v>
@@ -6786,7 +6786,11 @@
           <t>Private placements</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -7541,7 +7545,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E100" s="5" t="n">
         <v>-0.003639</v>
       </c>
@@ -7621,7 +7629,11 @@
           <t>Private placement</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E102" s="5" t="n">
         <v>0.36</v>
       </c>
@@ -8334,7 +8346,11 @@
           <t>Private placement</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E119" s="5" t="n">
         <v>0.36</v>
       </c>
@@ -8885,7 +8901,11 @@
           <t>Director fees 10</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>
@@ -9039,7 +9059,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E136" s="5" t="n">
         <v>0.002713</v>
       </c>
@@ -9505,7 +9529,11 @@
           <t>Director fees 14</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
           <t>-</t>
